--- a/Hoadon/HDVao/1/3502386218_HDDienTuDaCapMa.xlsx
+++ b/Hoadon/HDVao/1/3502386218_HDDienTuDaCapMa.xlsx
@@ -213,7 +213,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Từ ngày 01/01/2026 đến ngày 31/01/2026</t>
+          <t>Từ ngày 01/01/2026 đến ngày 03/01/2026</t>
         </is>
       </c>
     </row>
@@ -311,6 +311,89 @@
       <c r="S6" s="3" t="inlineStr">
         <is>
           <t>Kết quả kiểm tra hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>C26TPL</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>02/01/2026</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>0309414020</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ XÂY DỰNG PHAN LÊ</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>A-107 Khu nhà ở và nghỉ ngơi giải trí, đường số 5, Phường Tân Hưng, TP Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I7" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J7" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K7" s="13" t="n">
+        <v>3.31909091E8</v>
+      </c>
+      <c r="L7" s="13" t="n">
+        <v>3.3190909E7</v>
+      </c>
+      <c r="M7" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N7" s="13"/>
+      <c r="O7" s="13" t="n">
+        <v>3.651E8</v>
+      </c>
+      <c r="P7" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q7" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R7" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S7" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
         </is>
       </c>
     </row>

--- a/Hoadon/HDVao/1/3502386218_HDDienTuDaCapMa.xlsx
+++ b/Hoadon/HDVao/1/3502386218_HDDienTuDaCapMa.xlsx
@@ -325,32 +325,32 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>C26TPL</t>
+          <t>C26TBB</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>588</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>02/01/2026</t>
+          <t>06/01/2026</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>0309414020</t>
+          <t>0107581903-001</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ XÂY DỰNG PHAN LÊ</t>
+          <t>CÔNG TY TNHH BRITISH COUNCIL (VIỆT NAM) - CHI NHÁNH TP.HCM</t>
         </is>
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>A-107 Khu nhà ở và nghỉ ngơi giải trí, đường số 5, Phường Tân Hưng, TP Hồ Chí Minh, Việt Nam</t>
+          <t>285 Cách Mạng Tháng Tám, Phường Hòa Hưng, Thành phố Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I7" s="7" t="inlineStr">
@@ -364,17 +364,17 @@
         </is>
       </c>
       <c r="K7" s="13" t="n">
-        <v>3.31909091E8</v>
+        <v>3740741.0</v>
       </c>
       <c r="L7" s="13" t="n">
-        <v>3.3190909E7</v>
+        <v>299259.0</v>
       </c>
       <c r="M7" s="13" t="n">
-        <v>0.0</v>
+        <v>300000.0</v>
       </c>
       <c r="N7" s="13"/>
       <c r="O7" s="13" t="n">
-        <v>3.651E8</v>
+        <v>4040000.0</v>
       </c>
       <c r="P7" s="7" t="inlineStr">
         <is>
@@ -408,32 +408,32 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>C26TTA</t>
+          <t>C26TPL</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>05/01/2026</t>
+          <t>02/01/2026</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>3502452340</t>
+          <t>0309414020</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH HƯỚNG NGHIỆP VÀ ĐẠI LÝ THUẾ TÂM AN</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ XÂY DỰNG PHAN LÊ</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>205/12B Trương Công Định, phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>A-107 Khu nhà ở và nghỉ ngơi giải trí, đường số 5, Phường Tân Hưng, TP Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I8" s="7" t="inlineStr">
@@ -447,32 +447,115 @@
         </is>
       </c>
       <c r="K8" s="13" t="n">
-        <v>1.5E7</v>
+        <v>3.31909091E8</v>
       </c>
       <c r="L8" s="13" t="n">
-        <v>1200000.0</v>
-      </c>
-      <c r="M8" s="13"/>
+        <v>3.3190909E7</v>
+      </c>
+      <c r="M8" s="13" t="n">
+        <v>0.0</v>
+      </c>
       <c r="N8" s="13"/>
       <c r="O8" s="13" t="n">
+        <v>3.651E8</v>
+      </c>
+      <c r="P8" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q8" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R8" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S8" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>C26TTA</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>05/01/2026</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>3502452340</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH HƯỚNG NGHIỆP VÀ ĐẠI LÝ THUẾ TÂM AN</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>205/12B Trương Công Định, phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I9" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J9" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K9" s="13" t="n">
+        <v>1.5E7</v>
+      </c>
+      <c r="L9" s="13" t="n">
+        <v>1200000.0</v>
+      </c>
+      <c r="M9" s="13"/>
+      <c r="N9" s="13"/>
+      <c r="O9" s="13" t="n">
         <v>1.62E7</v>
       </c>
-      <c r="P8" s="7" t="inlineStr">
+      <c r="P9" s="7" t="inlineStr">
         <is>
           <t>VND</t>
         </is>
       </c>
-      <c r="Q8" s="7" t="inlineStr">
+      <c r="Q9" s="7" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="R8" s="6" t="inlineStr">
+      <c r="R9" s="6" t="inlineStr">
         <is>
           <t>Hóa đơn mới</t>
         </is>
       </c>
-      <c r="S8" s="6" t="inlineStr">
+      <c r="S9" s="6" t="inlineStr">
         <is>
           <t>Đã cấp mã hóa đơn</t>
         </is>
